--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.28917822273369</v>
+        <v>9.796991461194224</v>
       </c>
       <c r="D2" t="n">
-        <v>70.37546681295748</v>
+        <v>11.43601335710559</v>
       </c>
       <c r="E2" t="n">
-        <v>5.582612419366708</v>
+        <v>0.90717451814709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4886915338486943</v>
+        <v>0.07941237425041248</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.4544030614671</v>
+        <v>11.6113404974884</v>
       </c>
       <c r="D3" t="n">
-        <v>71.35284988065487</v>
+        <v>11.59483810560642</v>
       </c>
       <c r="E3" t="n">
-        <v>5.582612419366708</v>
+        <v>0.90717451814709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4886915338486943</v>
+        <v>0.07941237425041248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
